--- a/data/G7 Commands List.xlsx
+++ b/data/G7 Commands List.xlsx
@@ -1,26 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories\Serial-Opcode-Sender-LabVIEW\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repositories\Serial-Opcode-Sender-LabVIEW\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BC1714F-7CBF-48CD-BD63-B8C0D2177C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52476782-9590-4426-AA25-89E76122B53E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1236" yWindow="1116" windowWidth="17280" windowHeight="12300" xr2:uid="{4B944086-30BA-48E8-9A36-5C26F7877D52}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4B944086-30BA-48E8-9A36-5C26F7877D52}"/>
   </bookViews>
   <sheets>
     <sheet name="G7 Commands List" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_Hlk211496591" localSheetId="0">'G7 Commands List'!$B$32</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="77">
   <si>
     <t>command name</t>
   </si>
@@ -203,6 +206,123 @@
   </si>
   <si>
     <t>AA 09 7E 01 00 00 E8 03 00 00 9D</t>
+  </si>
+  <si>
+    <t>PKI 1: Patch Sequence Length</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKI 2: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKI 3: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PKI 4: </t>
+  </si>
+  <si>
+    <t>PKI 5:</t>
+  </si>
+  <si>
+    <t>PKI 6:</t>
+  </si>
+  <si>
+    <t>PKI 7:</t>
+  </si>
+  <si>
+    <t>PKI 8:</t>
+  </si>
+  <si>
+    <t>AA 6D 5F 0A 03 C8 C7 D6 B2 2C 68 02 F6 C0 45 D0 0A 46 BF 37 E1 05 CB 57 A4 E5 CC 3E E9 F4 35 14 38 38 97 37 78 AA 17 0C ED B6 A3 60 30 5E 30 0C 06 03 55 1D 13 01 01 FF 04 02 30 00 30 1D 06 03 55 1D 0E 04 16 04 14 99 50 0A FE 3E 40 4E 81 6F E4 33 2A CA A1 7D 6A 91 16 F8 E9 30 1F 06 03 55 1D 23 04 18 30 16 80 14 D0 D5 6F EB 7D 94 AD</t>
+  </si>
+  <si>
+    <t>AA 6D 5F 73 03 F4 53 5A A0 CA DD 41 28 35 36 CB 3A A2 BF 30 0E 06 03 55 1D 0F 01 01 FF 04 04 03 02 03 88 30 0A 06 08 2A 86 48 CE 3D 04 03 02 03 49 00 30 46 02 21 00 E8 44 BE 6A 6A 2C F6 7D DA FE 09 C1 AB 64 FB 25 5A 37 E5 63 1A C5 5E 20 D8 16 D7 C2 E2 7C B7 D8 02 21 00 DC 42 7B 70 76 76 CA D9 90 08 FE D0 91 0E 6C ED 78 18 21 58 82</t>
+  </si>
+  <si>
+    <t>AA 6D 5F DC 03 13 CF 74 25 B7 2D 2E 6F 6E D5 ED 77 04 79 30 77 02 01 01 04 20 83 42 AD 13 D1 D4 3B FB 92 3E 01 7C A3 AA 81 62 75 D4 11 BB B5 99 EA 24 91 69 7C 0D C2 36 48 B0 A0 0A 06 08 2A 86 48 CE 3D 03 01 07 A1 44 03 42 00 04 C1 8B ED 9E 9C D7 5A FE E0 A1 20 13 02 98 F1 79 18 C6 59 8F 8E C7 D7 AD CA D4 F0 C8 C7 D6 B2 2C 68 02 33</t>
+  </si>
+  <si>
+    <t>AA 46 5F 45 04 F6 C0 45 D0 0A 46 BF 37 E1 05 CB 57 A4 E5 CC 3E E9 F4 35 14 38 38 97 37 78 AA 17 0C ED B6 04 10 47 55 E8 3B 1A 0D 24 84 57 F8 14 15 5F 92 26 CA 04 10 FA 57 3F 66 B7 18 F7 76 2D 94 2D D5 55 86 0B 87 C7</t>
+  </si>
+  <si>
+    <t>AA 04 5F 87 04 D8</t>
+  </si>
+  <si>
+    <r>
+      <t>AA 06</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5F 02 00 04 83 DC</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AA 6D</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5F 38 02 04 82 01 AC 30 82 01 A8 30 82 01 4D A0 03 02 01 02 02 14 0F 56 83 A7 BB 88 7A A4 07 1D B9 B9 A2 01 BA 61 5C 70 4D A5 30 0A 06 08 2A 86 48 CE 3D 04 03 02 30 13 31 11 30 0F 06 03 55 04 03 0C 08 44 45 58 30 31 50 47 32 30 1E 17 0D 32 35 31 30 30 39 31 37 32 39 32 35 5A 17 0D 32 37 31 30 30 39 31 37 32 39 32 35 5A 30 6C</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>AA 6D</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5F A1 02 32 31 30 30 2E 06 03 55 04 03 0C 27 30 30 2C 30 30 30 30 2C 30 30 30 30 30 30 30 30 2C 38 50 45 43 41 77 41 42 41 67 4D 41 41 51 49 44 41 41 50 52 4F 44 30 59 30 13 06 07 2A 86 48 CE 3D 02 01 06 08 2A 86 48 CE 3D 03 01 07 03 42 00 04 C1 8B ED 9E 9C D7 5A FE E0 A1 20 13 02 98 F1 79 18 C6 59 8F 8E C7 D7 AD CA D4 F0 EC</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -704,11 +824,18 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1084,11 +1211,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A1A2F9-EB88-4036-A12E-635F91F6E518}">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="57.88671875" customWidth="1"/>
-    <col min="2" max="2" width="54.109375" customWidth="1"/>
+    <col min="2" max="2" width="66.21875" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
   </cols>
@@ -1408,6 +1535,70 @@
         <v>12</v>
       </c>
     </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A31" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="72" x14ac:dyDescent="0.3">
+      <c r="A32" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A33" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A34" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="72" x14ac:dyDescent="0.3">
+      <c r="A35" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>73</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
